--- a/data/trans_dic/IP17-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,94; 26,36</t>
+          <t>14,81; 25,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,27; 29,2</t>
+          <t>17,98; 29,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,73; 23,92</t>
+          <t>12,82; 24,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,86; 20,82</t>
+          <t>9,94; 20,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,67; 26,74</t>
+          <t>15,72; 26,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,71; 27,1</t>
+          <t>15,53; 26,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,96; 27,13</t>
+          <t>15,14; 26,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,23; 21,96</t>
+          <t>10,26; 21,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,19; 24,84</t>
+          <t>16,77; 24,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,1; 26,48</t>
+          <t>18,24; 26,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,72; 23,97</t>
+          <t>15,69; 23,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,28; 19,3</t>
+          <t>11,54; 19,73</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,48; 27,7</t>
+          <t>18,37; 28,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,23; 27,23</t>
+          <t>18,45; 27,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,46; 30,02</t>
+          <t>20,91; 30,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,31; 20,27</t>
+          <t>11,35; 20,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,17; 27,23</t>
+          <t>17,83; 27,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,29; 28,39</t>
+          <t>19,39; 28,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,41; 26,29</t>
+          <t>17,47; 26,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,69; 24,24</t>
+          <t>15,19; 24,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,4; 25,98</t>
+          <t>19,5; 25,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,06; 26,73</t>
+          <t>19,91; 26,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,13; 26,49</t>
+          <t>20,31; 26,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,94; 21,38</t>
+          <t>14,52; 20,83</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,09; 22,23</t>
+          <t>12,73; 23,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,14; 27,21</t>
+          <t>16,03; 26,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,85; 24,65</t>
+          <t>15,14; 24,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,03; 20,37</t>
+          <t>8,59; 20,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,6; 28,31</t>
+          <t>17,64; 28,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,06; 31,75</t>
+          <t>20,71; 31,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,1; 23,64</t>
+          <t>14,12; 23,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,62; 23,51</t>
+          <t>12,04; 23,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,75; 23,93</t>
+          <t>16,31; 23,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,54; 27,56</t>
+          <t>19,64; 27,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,08; 22,8</t>
+          <t>15,65; 22,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,41; 19,69</t>
+          <t>11,28; 19,57</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,28; 22,58</t>
+          <t>13,97; 22,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,53; 29,86</t>
+          <t>19,71; 29,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,55; 22,38</t>
+          <t>13,36; 22,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,48; 22,05</t>
+          <t>12,43; 21,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,75; 27,98</t>
+          <t>18,74; 28,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,79; 26,16</t>
+          <t>16,34; 25,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,92; 23,57</t>
+          <t>13,94; 22,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,84; 21,0</t>
+          <t>11,49; 20,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,34; 23,99</t>
+          <t>17,05; 23,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,46; 26,21</t>
+          <t>18,83; 26,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,18; 21,24</t>
+          <t>14,95; 21,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,0; 19,67</t>
+          <t>13,1; 19,49</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,38; 22,11</t>
+          <t>17,17; 21,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,19; 25,42</t>
+          <t>20,5; 25,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,03; 22,98</t>
+          <t>18,26; 23,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,55; 17,93</t>
+          <t>12,61; 18,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,96; 24,96</t>
+          <t>19,83; 24,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,18; 25,27</t>
+          <t>20,22; 25,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,19; 22,11</t>
+          <t>17,47; 22,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,09; 19,64</t>
+          <t>14,87; 19,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,4; 22,84</t>
+          <t>19,32; 22,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,05; 24,67</t>
+          <t>21,02; 24,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,44; 21,8</t>
+          <t>18,33; 21,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 18,06</t>
+          <t>14,46; 18,2</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>28082</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>32299</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23928</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17054</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32127</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>32413</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>30745</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>21666</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>60209</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>64712</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>54673</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>38720</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>20549; 35559</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25053; 41501</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17060; 32638</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11653; 24113</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>24065; 39843</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>23869; 41232</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>22426; 39605</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>14410; 30439</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>48928; 71588</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>53437; 77152</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>44119; 66318</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>29739; 50832</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>44763</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46851</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>52244</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28975</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>47746</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>52445</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>47923</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>49736</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>92509</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>99296</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>100167</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>78711</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>35857; 54673</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>37940; 56981</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43185; 62756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>21614; 38535</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>37820; 57954</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>43270; 63840</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>39057; 59266</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>38732; 61939</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>79444; 105489</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>85399; 115033</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>87369; 114269</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>64697; 92821</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>23496</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32786</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30574</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26236</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34003</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>42609</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>30391</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>31680</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>57499</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>75395</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>60965</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>57917</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>17537; 31766</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>24904; 41058</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23617; 38282</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16277; 39698</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>26398; 42157</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>34366; 52203</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>23365; 38882</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>22303; 42622</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>46888; 68526</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>63127; 87726</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>50326; 73098</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>42297; 73352</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>37247</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>51209</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>37141</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28049</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>47960</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>43114</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37060</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>28510</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>85207</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>94323</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>74201</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>56559</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>29240; 46984</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>41296; 61789</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>27705; 47617</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>20885; 36586</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>38938; 58813</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>34056; 53735</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>28386; 46692</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>20819; 37658</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>71101; 98374</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>78711; 109403</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>61450; 88227</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>45733; 68057</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>133587</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>163145</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>143886</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>100314</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>161836</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>170581</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>146119</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>131592</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>295424</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>333726</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>290005</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>231906</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>116961; 149439</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145520; 180809</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>128350; 163278</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>83926; 120598</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>143277; 179505</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>151924; 189534</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>129406; 164987</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>113277; 149728</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>271234; 317509</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>307151; 360128</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>264740; 313988</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>206386; 259768</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP17-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,81; 25,63</t>
+          <t>14,94; 26,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,98; 29,78</t>
+          <t>17,95; 29,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,82; 24,52</t>
+          <t>12,92; 24,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,94; 20,56</t>
+          <t>9,93; 20,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,72; 26,03</t>
+          <t>16,24; 26,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,53; 26,83</t>
+          <t>15,73; 26,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,14; 26,75</t>
+          <t>15,04; 27,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,26; 21,68</t>
+          <t>10,24; 22,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,77; 24,53</t>
+          <t>17,3; 24,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,24; 26,33</t>
+          <t>18,23; 26,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,69; 23,59</t>
+          <t>15,56; 23,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,54; 19,73</t>
+          <t>11,47; 19,15</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,37; 28,01</t>
+          <t>18,35; 28,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,45; 27,7</t>
+          <t>18,08; 27,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,91; 30,38</t>
+          <t>20,68; 30,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,35; 20,23</t>
+          <t>11,33; 20,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,83; 27,32</t>
+          <t>18,05; 27,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,39; 28,61</t>
+          <t>18,93; 28,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,47; 26,5</t>
+          <t>17,63; 26,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,19; 24,29</t>
+          <t>15,09; 24,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,5; 25,9</t>
+          <t>19,54; 25,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,91; 26,82</t>
+          <t>20,03; 26,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,31; 26,56</t>
+          <t>20,19; 26,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,52; 20,83</t>
+          <t>14,69; 20,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,73; 23,05</t>
+          <t>12,59; 22,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,03; 26,42</t>
+          <t>16,41; 26,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,14; 24,54</t>
+          <t>14,88; 24,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,59; 20,94</t>
+          <t>8,01; 20,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,64; 28,17</t>
+          <t>17,89; 28,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,71; 31,45</t>
+          <t>20,42; 31,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,12; 23,49</t>
+          <t>13,59; 23,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,04; 23,0</t>
+          <t>11,9; 22,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,31; 23,84</t>
+          <t>16,42; 23,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,64; 27,3</t>
+          <t>19,97; 27,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,65; 22,74</t>
+          <t>15,61; 22,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,28; 19,57</t>
+          <t>11,36; 19,96</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 22,45</t>
+          <t>13,61; 22,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,71; 29,49</t>
+          <t>19,47; 29,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,36; 22,96</t>
+          <t>13,84; 22,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,43; 21,78</t>
+          <t>12,53; 21,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,74; 28,3</t>
+          <t>18,42; 28,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,34; 25,79</t>
+          <t>16,34; 25,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,94; 22,93</t>
+          <t>13,96; 23,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,49; 20,78</t>
+          <t>11,54; 21,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,05; 23,58</t>
+          <t>17,47; 24,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,83; 26,18</t>
+          <t>19,08; 26,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,95; 21,46</t>
+          <t>14,98; 21,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,1; 19,49</t>
+          <t>13,02; 19,63</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,17; 21,94</t>
+          <t>17,17; 22,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,5; 25,47</t>
+          <t>20,46; 25,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,26; 23,22</t>
+          <t>18,16; 23,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,61; 18,13</t>
+          <t>12,34; 17,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,83; 24,84</t>
+          <t>19,86; 24,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,22; 25,23</t>
+          <t>20,17; 25,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,47; 22,27</t>
+          <t>17,53; 22,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,87; 19,65</t>
+          <t>14,87; 19,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,32; 22,62</t>
+          <t>19,4; 22,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,02; 24,65</t>
+          <t>21,06; 24,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,33; 21,75</t>
+          <t>18,47; 21,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 18,2</t>
+          <t>14,56; 18,08</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20549; 35559</t>
+          <t>20722; 37243</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25053; 41501</t>
+          <t>25014; 41542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17060; 32638</t>
+          <t>17198; 32346</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11653; 24113</t>
+          <t>11646; 23499</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24065; 39843</t>
+          <t>24861; 40810</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23869; 41232</t>
+          <t>24177; 41247</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22426; 39605</t>
+          <t>22271; 39986</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14410; 30439</t>
+          <t>14376; 31408</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48928; 71588</t>
+          <t>50487; 71968</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53437; 77152</t>
+          <t>53435; 77243</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44119; 66318</t>
+          <t>43761; 67242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29739; 50832</t>
+          <t>29566; 49343</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35857; 54673</t>
+          <t>35812; 54666</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37940; 56981</t>
+          <t>37195; 56948</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43185; 62756</t>
+          <t>42718; 62252</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21614; 38535</t>
+          <t>21576; 38615</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37820; 57954</t>
+          <t>38288; 57803</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43270; 63840</t>
+          <t>42253; 63865</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39057; 59266</t>
+          <t>39432; 58469</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38732; 61939</t>
+          <t>38493; 61545</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79444; 105489</t>
+          <t>79572; 105490</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85399; 115033</t>
+          <t>85891; 113752</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87369; 114269</t>
+          <t>86856; 113733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>64697; 92821</t>
+          <t>65442; 93257</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17537; 31766</t>
+          <t>17351; 30979</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24904; 41058</t>
+          <t>25499; 41418</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23617; 38282</t>
+          <t>23207; 38476</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16277; 39698</t>
+          <t>15194; 38079</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26398; 42157</t>
+          <t>26779; 42419</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34366; 52203</t>
+          <t>33895; 51482</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23365; 38882</t>
+          <t>22496; 38755</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22303; 42622</t>
+          <t>22049; 42353</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46888; 68526</t>
+          <t>47217; 68305</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63127; 87726</t>
+          <t>64165; 89045</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50326; 73098</t>
+          <t>50191; 71687</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42297; 73352</t>
+          <t>42567; 74836</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29240; 46984</t>
+          <t>28498; 47377</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41296; 61789</t>
+          <t>40804; 61186</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27705; 47617</t>
+          <t>28709; 47320</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20885; 36586</t>
+          <t>21039; 36591</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38938; 58813</t>
+          <t>38276; 58264</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34056; 53735</t>
+          <t>34045; 53199</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28386; 46692</t>
+          <t>28429; 47045</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20819; 37658</t>
+          <t>20918; 38161</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71101; 98374</t>
+          <t>72869; 100459</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78711; 109403</t>
+          <t>79729; 108893</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61450; 88227</t>
+          <t>61592; 89140</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45733; 68057</t>
+          <t>45453; 68547</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>116961; 149439</t>
+          <t>116903; 151293</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>145520; 180809</t>
+          <t>145285; 183629</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>128350; 163278</t>
+          <t>127645; 161928</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83926; 120598</t>
+          <t>82080; 116826</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>143277; 179505</t>
+          <t>143533; 179665</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>151924; 189534</t>
+          <t>151532; 188742</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>129406; 164987</t>
+          <t>129843; 164378</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>113277; 149728</t>
+          <t>113296; 151520</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>271234; 317509</t>
+          <t>272281; 320747</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>307151; 360128</t>
+          <t>307721; 361743</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>264740; 313988</t>
+          <t>266751; 316631</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>206386; 259768</t>
+          <t>207822; 258123</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP17-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Habitat-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20,99%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21,09%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15,92%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>20,24%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>23,18%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>17,98%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14,54%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,99%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,76%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,94; 26,85</t>
+          <t>15,67; 26,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,95; 29,81</t>
+          <t>15,71; 27,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,92; 24,3</t>
+          <t>15,96; 27,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,93; 20,04</t>
+          <t>10,4; 21,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,24; 26,66</t>
+          <t>14,94; 26,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,73; 26,84</t>
+          <t>17,27; 29,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,04; 27,0</t>
+          <t>12,73; 23,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 22,37</t>
+          <t>9,49; 20,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,3; 24,66</t>
+          <t>17,19; 24,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,23; 26,36</t>
+          <t>18,1; 26,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,56; 23,91</t>
+          <t>15,72; 23,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,47; 19,15</t>
+          <t>11,4; 19,54</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22,51%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21,43%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>22,94%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>22,78%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>25,29%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22,51%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>23,5%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>21,43%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,35; 28,01</t>
+          <t>18,17; 27,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,08; 27,69</t>
+          <t>19,29; 28,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,68; 30,14</t>
+          <t>17,41; 26,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,33; 20,27</t>
+          <t>15,32; 23,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,05; 27,25</t>
+          <t>18,48; 27,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,93; 28,62</t>
+          <t>18,23; 27,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,63; 26,15</t>
+          <t>20,46; 30,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,09; 24,13</t>
+          <t>10,67; 19,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,54; 25,9</t>
+          <t>19,4; 25,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,03; 26,53</t>
+          <t>20,06; 26,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,19; 26,44</t>
+          <t>20,13; 26,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,69; 20,93</t>
+          <t>14,42; 20,8</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22,72%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25,67%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18,36%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>17,05%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>21,1%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>19,6%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,67%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,59; 22,48</t>
+          <t>17,6; 28,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 26,66</t>
+          <t>21,06; 31,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,88; 24,66</t>
+          <t>14,1; 23,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,01; 20,09</t>
+          <t>13,4; 24,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,89; 28,34</t>
+          <t>12,09; 22,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,42; 31,02</t>
+          <t>16,14; 27,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,59; 23,42</t>
+          <t>14,85; 24,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,9; 22,86</t>
+          <t>10,75; 20,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,42; 23,76</t>
+          <t>16,75; 23,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,97; 27,71</t>
+          <t>19,54; 27,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,61; 22,3</t>
+          <t>16,08; 22,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,36; 19,96</t>
+          <t>13,08; 20,31</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23,08%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20,69%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15,41%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>17,79%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>24,44%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>17,91%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,2%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,61; 22,63</t>
+          <t>18,75; 27,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,47; 29,2</t>
+          <t>16,79; 26,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,84; 22,81</t>
+          <t>13,92; 23,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,53; 21,78</t>
+          <t>11,64; 20,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,42; 28,04</t>
+          <t>13,28; 22,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,34; 25,53</t>
+          <t>19,53; 29,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,96; 23,1</t>
+          <t>13,55; 22,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,54; 21,06</t>
+          <t>12,36; 21,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,47; 24,08</t>
+          <t>17,34; 23,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,08; 26,06</t>
+          <t>19,46; 26,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,98; 21,68</t>
+          <t>15,18; 21,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,02; 19,63</t>
+          <t>12,78; 19,27</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>22,39%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22,71%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>19,62%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>22,98%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>20,47%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>22,39%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>22,71%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,17; 22,22</t>
+          <t>19,96; 24,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,46; 25,86</t>
+          <t>20,18; 25,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,16; 23,03</t>
+          <t>17,19; 22,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,34; 17,56</t>
+          <t>15,03; 19,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,86; 24,86</t>
+          <t>17,38; 22,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,17; 25,13</t>
+          <t>20,19; 25,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,53; 22,19</t>
+          <t>18,03; 22,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,87; 19,89</t>
+          <t>13,0; 17,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,4; 22,85</t>
+          <t>19,4; 22,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,06; 24,76</t>
+          <t>21,05; 24,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,47; 21,93</t>
+          <t>18,44; 21,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,56; 18,08</t>
+          <t>14,73; 18,15</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32127</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>32413</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30745</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>28082</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>32299</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>23928</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>32127</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32413</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>30745</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20722; 37243</t>
+          <t>23989; 40929</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25014; 41542</t>
+          <t>24140; 41641</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17198; 32346</t>
+          <t>23633; 40167</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11646; 23499</t>
+          <t>13098; 27592</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24861; 40810</t>
+          <t>20722; 36568</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24177; 41247</t>
+          <t>24071; 40693</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22271; 39986</t>
+          <t>16940; 31844</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14376; 31408</t>
+          <t>11485; 24966</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50487; 71968</t>
+          <t>50156; 72477</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53435; 77243</t>
+          <t>53029; 77596</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43761; 67242</t>
+          <t>44207; 67400</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29566; 49343</t>
+          <t>28158; 48257</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>47746</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>52445</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47923</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>45393</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>44763</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>46851</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>52244</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>47746</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>52445</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>47923</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>72342</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35812; 54666</t>
+          <t>38540; 57765</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37195; 56948</t>
+          <t>43050; 63349</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42718; 62252</t>
+          <t>38931; 58791</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21576; 38615</t>
+          <t>36346; 56686</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38288; 57803</t>
+          <t>36066; 54063</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42253; 63865</t>
+          <t>37493; 56014</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39432; 58469</t>
+          <t>42266; 61999</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38493; 61545</t>
+          <t>19678; 35589</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79572; 105490</t>
+          <t>79019; 105807</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85891; 113752</t>
+          <t>86042; 114619</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86856; 113733</t>
+          <t>86578; 113950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65442; 93257</t>
+          <t>60801; 87705</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>34003</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>42609</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30391</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>23496</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>32786</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>30574</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>34003</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42609</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>30391</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>53901</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17351; 30979</t>
+          <t>26336; 42369</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25499; 41418</t>
+          <t>34950; 52690</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23207; 38476</t>
+          <t>23333; 39122</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15194; 38079</t>
+          <t>22551; 41590</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26779; 42419</t>
+          <t>16663; 30632</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33895; 51482</t>
+          <t>25072; 42272</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22496; 38755</t>
+          <t>23167; 38460</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22049; 42353</t>
+          <t>16792; 32034</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47217; 68305</t>
+          <t>48144; 68781</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64165; 89045</t>
+          <t>62795; 88550</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50191; 71687</t>
+          <t>51702; 73311</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42567; 74836</t>
+          <t>42449; 65902</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>47960</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>43114</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>37060</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>37247</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>51209</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>37141</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>47960</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43114</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37060</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>27702</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28498; 47377</t>
+          <t>38963; 58140</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40804; 61186</t>
+          <t>34982; 54506</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28709; 47320</t>
+          <t>28343; 47995</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21039; 36591</t>
+          <t>19714; 34636</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38276; 58264</t>
+          <t>27800; 47256</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34045; 53199</t>
+          <t>40933; 62563</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28429; 47045</t>
+          <t>28109; 46417</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20918; 38161</t>
+          <t>20664; 36604</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72869; 100459</t>
+          <t>72327; 100055</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79729; 108893</t>
+          <t>81323; 109552</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61592; 89140</t>
+          <t>62418; 87315</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45453; 68547</t>
+          <t>42996; 64836</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>223</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>153</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>161836</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>170581</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>146119</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>133587</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>163145</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>143886</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>161836</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>170581</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>146119</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>116903; 151293</t>
+          <t>144249; 180387</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>145285; 183629</t>
+          <t>151559; 189799</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>127645; 161928</t>
+          <t>127328; 163833</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>82080; 116826</t>
+          <t>105312; 138293</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>143533; 179665</t>
+          <t>118374; 150599</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>151532; 188742</t>
+          <t>143342; 180478</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>129843; 164378</t>
+          <t>126750; 161597</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>113296; 151520</t>
+          <t>81764; 111378</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>272281; 320747</t>
+          <t>272305; 320612</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>307721; 361743</t>
+          <t>307512; 360492</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>266751; 316631</t>
+          <t>266309; 314781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>207822; 258123</t>
+          <t>195795; 241364</t>
         </is>
       </c>
     </row>
